--- a/data/trans_orig/P36BPD11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023</t>
+          <t>Población según el número de veces que consumen repostería comercial a la semana en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>103606</t>
+          <t>102215</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167796</t>
+          <t>166817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100350</t>
+          <t>102741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146040</t>
+          <t>148821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219287</t>
+          <t>218185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>299958</t>
+          <t>297500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142925</t>
+          <t>141873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214132</t>
+          <t>214063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114051</t>
+          <t>112371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160620</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274068</t>
+          <t>270587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355691</t>
+          <t>355316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,82%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61621</t>
+          <t>62840</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122723</t>
+          <t>122255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35778</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>110544</t>
+          <t>108866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>177642</t>
+          <t>184748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158118</t>
+          <t>159108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209910</t>
+          <t>209642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107522</t>
+          <t>99126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208631</t>
+          <t>206003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276179</t>
+          <t>271585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400323</t>
+          <t>401925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144219</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>195030</t>
+          <t>193664</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200888</t>
+          <t>199777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>354599</t>
+          <t>352946</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>361010</t>
+          <t>361111</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>531847</t>
+          <t>540944</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53518</t>
+          <t>54966</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92979</t>
+          <t>95618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>57612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113613</t>
+          <t>116453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116569</t>
+          <t>121386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189862</t>
+          <t>191818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>212537</t>
+          <t>214031</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>260440</t>
+          <t>262098</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>235212</t>
+          <t>238470</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>274344</t>
+          <t>277151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>461286</t>
+          <t>462186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>525184</t>
+          <t>523620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179861</t>
+          <t>181709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227148</t>
+          <t>227182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190943</t>
+          <t>189969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228207</t>
+          <t>227354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>382963</t>
+          <t>386526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>443685</t>
+          <t>446860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77048</t>
+          <t>76507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114616</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61287</t>
+          <t>59970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87481</t>
+          <t>86788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149056</t>
+          <t>146810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192134</t>
+          <t>192646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>413700</t>
+          <t>409538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>742031</t>
+          <t>749991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289508</t>
+          <t>284931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>371867</t>
+          <t>371524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>754039</t>
+          <t>746640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1173019</t>
+          <t>1144940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98316</t>
+          <t>91766</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>317630</t>
+          <t>319944</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196232</t>
+          <t>194789</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>257348</t>
+          <t>256089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270604</t>
+          <t>287364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>552745</t>
+          <t>558169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165513</t>
+          <t>167925</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98513</t>
+          <t>99775</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231092</t>
+          <t>239029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156006</t>
+          <t>155101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>335605</t>
+          <t>331498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231492</t>
+          <t>232718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274597</t>
+          <t>276722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280909</t>
+          <t>279676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316063</t>
+          <t>315935</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524185</t>
+          <t>525438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>580942</t>
+          <t>582679</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>172061</t>
+          <t>172491</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>213154</t>
+          <t>215344</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>160429</t>
+          <t>161772</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194728</t>
+          <t>193478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>341176</t>
+          <t>343073</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>395928</t>
+          <t>398323</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97085</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131425</t>
+          <t>131191</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60560</t>
+          <t>60157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83429</t>
+          <t>84347</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>162468</t>
+          <t>163597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207297</t>
+          <t>208912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176678</t>
+          <t>175782</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207855</t>
+          <t>207047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>316933</t>
+          <t>317454</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>531001</t>
+          <t>532022</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>506585</t>
+          <t>508919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>802713</t>
+          <t>790306</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112080</t>
+          <t>112641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142576</t>
+          <t>142203</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53891</t>
+          <t>51615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208463</t>
+          <t>207648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121910</t>
+          <t>133788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>336905</t>
+          <t>336721</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37021</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>59520</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>87077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>48360</t>
+          <t>49310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134301</t>
+          <t>134134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141316</t>
+          <t>142032</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169764</t>
+          <t>169151</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>217101</t>
+          <t>216468</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>244249</t>
+          <t>245371</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>367872</t>
+          <t>366692</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>409023</t>
+          <t>407021</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>102882</t>
+          <t>101033</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128014</t>
+          <t>126887</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>155068</t>
+          <t>154650</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>209714</t>
+          <t>212004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>246085</t>
+          <t>250394</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>47268</t>
+          <t>48239</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>43461</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63327</t>
+          <t>64479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>78559</t>
+          <t>78817</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>104849</t>
+          <t>105808</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1551316</t>
+          <t>1560465</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2095125</t>
+          <t>2120679</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1705155</t>
+          <t>1699167</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2159875</t>
+          <t>2151185</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3325296</t>
+          <t>3324335</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4035101</t>
+          <t>4055399</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,01%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>921631</t>
+          <t>936617</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1294714</t>
+          <t>1290988</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1077364</t>
+          <t>1065539</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1411226</t>
+          <t>1414550</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2131153</t>
+          <t>2162248</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2643408</t>
+          <t>2652470</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>441437</t>
+          <t>437713</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>636436</t>
+          <t>631582</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>443238</t>
+          <t>445627</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>617538</t>
+          <t>625199</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>962760</t>
+          <t>958600</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1223539</t>
+          <t>1203347</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD11_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD11_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>133067</t>
+          <t>135277</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102215</t>
+          <t>107114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166817</t>
+          <t>167596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>124786</t>
+          <t>141387</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102741</t>
+          <t>117275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148821</t>
+          <t>167866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,22 +795,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>257853</t>
+          <t>276665</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218185</t>
+          <t>235672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>297500</t>
+          <t>317126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>178526</t>
+          <t>179430</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141873</t>
+          <t>146619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214063</t>
+          <t>213990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>155402</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112371</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159364</t>
+          <t>180628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>314499</t>
+          <t>334832</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270587</t>
+          <t>290484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355316</t>
+          <t>373599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88394</t>
+          <t>93085</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>122255</t>
+          <t>122563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>65723</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>46762</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>87666</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>140835</t>
+          <t>158808</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108866</t>
+          <t>125136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184748</t>
+          <t>198563</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>184467</t>
+          <t>216266</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159108</t>
+          <t>189883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209642</t>
+          <t>242951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>171949</t>
+          <t>199909</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99126</t>
+          <t>176802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206003</t>
+          <t>223103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>356415</t>
+          <t>416176</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271585</t>
+          <t>379513</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401925</t>
+          <t>454823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>168003</t>
+          <t>181073</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141507</t>
+          <t>153465</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193664</t>
+          <t>207580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249015</t>
+          <t>195703</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>199777</t>
+          <t>174221</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>352946</t>
+          <t>218189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>417019</t>
+          <t>376776</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>361111</t>
+          <t>338807</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>540944</t>
+          <t>414009</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71077</t>
+          <t>79551</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54966</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95618</t>
+          <t>102068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>105471</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57612</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116453</t>
+          <t>127368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>161617</t>
+          <t>185022</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121386</t>
+          <t>156244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191818</t>
+          <t>216680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>236657</t>
+          <t>270420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214031</t>
+          <t>245798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>297926</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257325</t>
+          <t>292363</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238470</t>
+          <t>272389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>277151</t>
+          <t>313093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>493981</t>
+          <t>562782</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>462186</t>
+          <t>527385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>523620</t>
+          <t>596323</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,09%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204097</t>
+          <t>237903</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181709</t>
+          <t>214665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227182</t>
+          <t>265864</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>208834</t>
+          <t>239119</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189969</t>
+          <t>217024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227354</t>
+          <t>258553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>412931</t>
+          <t>477022</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>386526</t>
+          <t>444176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>446860</t>
+          <t>508355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95584</t>
+          <t>112515</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76507</t>
+          <t>92473</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>135248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>73545</t>
+          <t>87733</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59970</t>
+          <t>73351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86788</t>
+          <t>104483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>169129</t>
+          <t>200248</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146810</t>
+          <t>176104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192646</t>
+          <t>228205</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>539703</t>
+          <t>619215</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>539703</t>
+          <t>619215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>539703</t>
+          <t>619215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1076041</t>
+          <t>1240052</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1076041</t>
+          <t>1240052</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1076041</t>
+          <t>1240052</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>551119</t>
+          <t>336368</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>409538</t>
+          <t>309099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>749991</t>
+          <t>363971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>345016</t>
+          <t>366979</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284931</t>
+          <t>346482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>371524</t>
+          <t>390219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>896136</t>
+          <t>703347</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>746640</t>
+          <t>670054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1144940</t>
+          <t>741948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>51,63%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>222904</t>
+          <t>238827</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91766</t>
+          <t>213563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319944</t>
+          <t>266047</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>234364</t>
+          <t>257447</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194789</t>
+          <t>234779</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256089</t>
+          <t>277734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>457268</t>
+          <t>496274</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287364</t>
+          <t>464007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558169</t>
+          <t>528467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>113763</t>
+          <t>125422</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>103489</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167925</t>
+          <t>146461</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>133118</t>
+          <t>112068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99775</t>
+          <t>98354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>239029</t>
+          <t>128390</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>246881</t>
+          <t>237490</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>155101</t>
+          <t>213207</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331498</t>
+          <t>265218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>254447</t>
+          <t>279779</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232718</t>
+          <t>256137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276722</t>
+          <t>301932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>297905</t>
+          <t>330810</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>279676</t>
+          <t>310528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>315935</t>
+          <t>351522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>552352</t>
+          <t>610589</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525438</t>
+          <t>582777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>582679</t>
+          <t>641831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>192851</t>
+          <t>209528</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>172491</t>
+          <t>188553</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>215344</t>
+          <t>231846</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>177423</t>
+          <t>198342</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>161772</t>
+          <t>181303</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193478</t>
+          <t>216809</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>370274</t>
+          <t>407870</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>343073</t>
+          <t>377297</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>398323</t>
+          <t>435980</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>112742</t>
+          <t>117340</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>99486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131191</t>
+          <t>135467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>71270</t>
+          <t>78255</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>66730</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84347</t>
+          <t>91261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>184012</t>
+          <t>195595</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163597</t>
+          <t>173558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208912</t>
+          <t>219233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560040</t>
+          <t>606647</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560040</t>
+          <t>606647</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560040</t>
+          <t>606647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>546598</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546598</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>546598</t>
+          <t>607407</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1106638</t>
+          <t>1214054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1106638</t>
+          <t>1214054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1106638</t>
+          <t>1214054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>192321</t>
+          <t>212620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175782</t>
+          <t>196460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>207047</t>
+          <t>229752</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>419492</t>
+          <t>235270</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>317454</t>
+          <t>220524</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>532022</t>
+          <t>250213</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>611813</t>
+          <t>447890</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>508919</t>
+          <t>423382</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>790306</t>
+          <t>470290</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>126948</t>
+          <t>137629</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112641</t>
+          <t>122020</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142203</t>
+          <t>153595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>133958</t>
+          <t>144079</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51615</t>
+          <t>129593</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207648</t>
+          <t>157945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>260906</t>
+          <t>281708</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>133788</t>
+          <t>259874</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>336721</t>
+          <t>302001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -3231,69 +3231,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>55250</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59520</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>59464</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>50247</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>71209</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>16,23%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>54531</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>21480</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>87077</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>191</t>
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>101969</t>
+          <t>114713</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>101067</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>134134</t>
+          <t>130200</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>366707</t>
+          <t>405499</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>366707</t>
+          <t>405499</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>366707</t>
+          <t>405499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>607981</t>
+          <t>438813</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>607981</t>
+          <t>438813</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>607981</t>
+          <t>438813</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>974688</t>
+          <t>844311</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>974688</t>
+          <t>844311</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>974688</t>
+          <t>844311</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>155940</t>
+          <t>170477</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>142032</t>
+          <t>155448</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169151</t>
+          <t>184525</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>231597</t>
+          <t>252797</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>216468</t>
+          <t>237155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>245371</t>
+          <t>267827</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387537</t>
+          <t>423275</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>366692</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>407021</t>
+          <t>445395</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,54%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>89192</t>
+          <t>96921</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>83920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>101033</t>
+          <t>110794</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>139991</t>
+          <t>152895</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>126887</t>
+          <t>139961</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>154650</t>
+          <t>168693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>229183</t>
+          <t>249816</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212004</t>
+          <t>228635</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>250394</t>
+          <t>268589</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37627</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>33121</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48239</t>
+          <t>54398</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,67 +3722,67 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53495</t>
+          <t>58121</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43461</t>
+          <t>48661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>64479</t>
+          <t>69205</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>100922</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>87805</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>117407</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>15,17%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>91122</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>78817</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>105808</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425083</t>
+          <t>463814</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425083</t>
+          <t>463814</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425083</t>
+          <t>463814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>707842</t>
+          <t>774013</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>707842</t>
+          <t>774013</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>707842</t>
+          <t>774013</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1708017</t>
+          <t>1621208</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1560465</t>
+          <t>1552429</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2120679</t>
+          <t>1683890</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1848070</t>
+          <t>1819517</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1699167</t>
+          <t>1760876</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2151185</t>
+          <t>1869046</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3556088</t>
+          <t>3440725</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3324335</t>
+          <t>3358972</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4055399</t>
+          <t>3518196</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1182522</t>
+          <t>1281311</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>936617</t>
+          <t>1217939</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1290988</t>
+          <t>1344833</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1279558</t>
+          <t>1342987</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1065539</t>
+          <t>1289892</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1414550</t>
+          <t>1398694</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2462079</t>
+          <t>2624298</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2162248</t>
+          <t>2548013</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2652470</t>
+          <t>2716157</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>566626</t>
+          <t>625963</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>437713</t>
+          <t>574518</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>631582</t>
+          <t>681426</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>528940</t>
+          <t>566836</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>445627</t>
+          <t>525036</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>625199</t>
+          <t>606701</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1095566</t>
+          <t>1192799</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>958600</t>
+          <t>1126219</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1203347</t>
+          <t>1259873</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3457165</t>
+          <t>3528482</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3656568</t>
+          <t>3729340</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7113733</t>
+          <t>7257822</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
